--- a/03-northgate-signal-fedramp-20x/artifacts/ksi_validation_register.xlsx
+++ b/03-northgate-signal-fedramp-20x/artifacts/ksi_validation_register.xlsx
@@ -521,7 +521,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -646,7 +645,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="68.65000000000001" customHeight="1" s="11">
+    <row r="6" ht="100" customHeight="1" s="11">
       <c r="A6" s="15" t="inlineStr">
         <is>
           <t>KSI-IAM-APM</t>
@@ -669,7 +668,7 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>AC-03, IA-02, IA-02(01), IA-02(02), IA-02(08), IA-05, IA-05(01), IA-05(02), IA-05(06), IA-06</t>
+          <t>AC-03, IA-02, IA-02(01), IA-02(02), IA-02(08), IA-05, IA-05(01), IA-05(02), IA-05(06), IA-06, IA-08, SC-23, AC-02</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -708,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="35.05" customHeight="1" s="11">
+    <row r="7" ht="100" customHeight="1" s="11">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>KSI-IAM-ELP</t>
@@ -731,7 +730,7 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>AC-02(05), AC-02(06), AC-03, AC-04, AC-06, AC-12, AC-17, AC-20, IA-02, IA-03</t>
+          <t>AC-02(05), AC-02(06), AC-03, AC-04, AC-06, AC-12, AC-17, AC-20, IA-02, IA-03, IA-11, SI-03</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -770,7 +769,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="46.25" customHeight="1" s="11">
+    <row r="8" ht="100" customHeight="1" s="11">
       <c r="A8" s="15" t="inlineStr">
         <is>
           <t>KSI-IAM-JIT</t>
@@ -793,7 +792,7 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>AC-02, AC-02(01), AC-05, AC-06, AC-06(01), AC-06(02), AC-06(05), AC-06(09), AC-06(10), CM-05</t>
+          <t>AC-02, AC-02(01), AC-05, AC-06, AC-06(01), AC-06(02), AC-06(05), AC-06(09), AC-06(10), CM-05, CM-07, SC-02</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
@@ -1402,7 +1401,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1579,7 +1577,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="11">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -1769,7 +1766,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="23.85" customHeight="1" s="11">
       <c r="A3" s="17" t="inlineStr">
         <is>
